--- a/data/trans_orig/P39B_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P39B_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según lo que piensan que es lo mejor que se puede hacer cuando creen que a alguien le está dando un ataque al corazón en 2023</t>
+          <t>Población según lo que piensan que es lo mejor que se puede hacer cuando creen que a alguien le está dando un ataque al corazón en 2023 (tasa de respuesta: 97,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>2348</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13442</t>
+          <t>13000</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1615</t>
+          <t>1563</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7999</t>
+          <t>8092</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5509</t>
+          <t>5045</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17492</t>
+          <t>17304</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>987</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9633</t>
+          <t>10086</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10028</t>
+          <t>9526</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>3133</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15189</t>
+          <t>15520</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>465931</t>
+          <t>466215</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>485116</t>
+          <t>485256</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>422919</t>
+          <t>423069</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>435861</t>
+          <t>435563</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>895630</t>
+          <t>894716</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>918733</t>
+          <t>917873</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2863</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15773</t>
+          <t>16617</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>434</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4852</t>
+          <t>5289</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4244</t>
+          <t>4470</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19396</t>
+          <t>17800</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>1471</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9161</t>
+          <t>9156</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1633</t>
+          <t>1624</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9038</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4396</t>
+          <t>4084</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14355</t>
+          <t>14670</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2294</t>
+          <t>2346</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11970</t>
+          <t>11929</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1645</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8512</t>
+          <t>9355</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5229</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16371</t>
+          <t>15885</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9079</t>
+          <t>9912</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9777</t>
+          <t>9997</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13707</t>
+          <t>13575</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>424038</t>
+          <t>423711</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>439549</t>
+          <t>439215</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>354648</t>
+          <t>355101</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>369822</t>
+          <t>369913</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>784585</t>
+          <t>784799</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>806044</t>
+          <t>806360</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1679</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13552</t>
+          <t>12726</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11673</t>
+          <t>11329</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17585</t>
+          <t>18145</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>453</t>
+          <t>609</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>6784</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1248</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9402</t>
+          <t>8122</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2351</t>
+          <t>2431</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10734</t>
+          <t>11380</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1734</t>
+          <t>1540</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17458</t>
+          <t>16615</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>573</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5334</t>
+          <t>5122</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18666</t>
+          <t>18435</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>4937</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4571</t>
+          <t>4060</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>498</t>
+          <t>484</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6476</t>
+          <t>6407</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>610956</t>
+          <t>609293</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>651972</t>
+          <t>650471</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>146061</t>
+          <t>147507</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>157501</t>
+          <t>157562</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>762867</t>
+          <t>764110</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>807557</t>
+          <t>812563</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24539</t>
+          <t>26266</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4605</t>
+          <t>4650</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13512</t>
+          <t>12995</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8313</t>
+          <t>7533</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34933</t>
+          <t>33766</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>773</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13525</t>
+          <t>14145</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2401</t>
+          <t>2738</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>1420</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13705</t>
+          <t>13437</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>3608</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14743</t>
+          <t>14523</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15565</t>
+          <t>16166</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9986</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25294</t>
+          <t>25756</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9953</t>
+          <t>10249</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>32797</t>
+          <t>34744</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2668</t>
+          <t>2593</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12688</t>
+          <t>12723</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,47 +2939,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>25850</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>15670</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>40523</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
           <t>1,31%</t>
         </is>
       </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>25850</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>14124</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>40310</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>909212</t>
+          <t>909839</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>946060</t>
+          <t>946122</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>918973</t>
+          <t>918558</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>950074</t>
+          <t>950742</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1837463</t>
+          <t>1836805</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1895990</t>
+          <t>1897217</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32829</t>
+          <t>32316</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56934</t>
+          <t>58087</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8135</t>
+          <t>7578</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25906</t>
+          <t>26633</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>41718</t>
+          <t>40788</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>77663</t>
+          <t>79099</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8789</t>
+          <t>8505</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21493</t>
+          <t>22470</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8903</t>
+          <t>8420</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>23233</t>
+          <t>23623</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6681</t>
+          <t>6292</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>4582</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14105</t>
+          <t>13876</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5376</t>
+          <t>5498</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16928</t>
+          <t>15632</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1159</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8771</t>
+          <t>8718</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2930</t>
+          <t>2934</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10185</t>
+          <t>10813</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3626,7 +3626,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5427</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15071</t>
+          <t>15630</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>393525</t>
+          <t>394029</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>418235</t>
+          <t>418439</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>734447</t>
+          <t>735937</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>766966</t>
+          <t>767882</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1136726</t>
+          <t>1139561</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1177347</t>
+          <t>1181052</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,65%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>16108</t>
+          <t>16799</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>37272</t>
+          <t>36143</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>25322</t>
+          <t>24480</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>46890</t>
+          <t>45815</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>46675</t>
+          <t>46243</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>77710</t>
+          <t>75863</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>7564</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>20406</t>
+          <t>21209</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>6050</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>18205</t>
+          <t>18215</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>15694</t>
+          <t>15683</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>34048</t>
+          <t>32921</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2411</t>
+          <t>2553</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>9446</t>
+          <t>9717</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2304</t>
+          <t>2522</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>9395</t>
+          <t>9591</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7144</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>18108</t>
+          <t>18273</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7291</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>18442</t>
+          <t>17901</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4343,7 +4343,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>212775</t>
+          <t>211374</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>230956</t>
+          <t>231511</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>662533</t>
+          <t>661796</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>686417</t>
+          <t>686040</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>883235</t>
+          <t>883724</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>913806</t>
+          <t>913744</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,01%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>12781</t>
+          <t>13164</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>16217</t>
+          <t>16096</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>34376</t>
+          <t>34961</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>19840</t>
+          <t>19314</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>41418</t>
+          <t>40504</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2814</t>
+          <t>2746</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>19080</t>
+          <t>20728</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>4912</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>14377</t>
+          <t>14920</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>9107</t>
+          <t>9923</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>28277</t>
+          <t>28422</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>19168</t>
+          <t>18225</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>40450</t>
+          <t>40874</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>22725</t>
+          <t>23350</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>41488</t>
+          <t>42159</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>46092</t>
+          <t>47520</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>76610</t>
+          <t>76254</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>20083</t>
+          <t>19143</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>48777</t>
+          <t>45869</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>23931</t>
+          <t>24217</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>44162</t>
+          <t>44004</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>49201</t>
+          <t>48765</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>82994</t>
+          <t>81474</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3074767</t>
+          <t>3070450</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>3152799</t>
+          <t>3151794</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3280748</t>
+          <t>3280498</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3340882</t>
+          <t>3339146</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>6362938</t>
+          <t>6363163</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>6466238</t>
+          <t>6466014</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,1%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>72185</t>
+          <t>75057</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>121524</t>
+          <t>122261</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>71536</t>
+          <t>71211</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>109313</t>
+          <t>107305</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>158214</t>
+          <t>158406</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>221402</t>
+          <t>216998</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>33296</t>
+          <t>32664</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>63639</t>
+          <t>62904</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>19767</t>
+          <t>19796</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>38027</t>
+          <t>38362</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>58929</t>
+          <t>58394</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>95345</t>
+          <t>94083</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P39B_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P39B_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6089</t>
+          <t>6017</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2348</t>
+          <t>2440</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13000</t>
+          <t>13129</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3790</t>
+          <t>4453</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1563</t>
+          <t>1768</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8092</t>
+          <t>8541</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9878</t>
+          <t>10470</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5045</t>
+          <t>5680</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17304</t>
+          <t>18495</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3638</t>
+          <t>4509</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10086</t>
+          <t>10925</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3305</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9526</t>
+          <t>10245</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>6943</t>
+          <t>7933</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>3518</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15520</t>
+          <t>16588</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>477445</t>
+          <t>522126</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>466215</t>
+          <t>511176</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>485256</t>
+          <t>530208</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>430915</t>
+          <t>469926</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>423069</t>
+          <t>462999</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>435563</t>
+          <t>474971</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>908360</t>
+          <t>992053</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>894716</t>
+          <t>977984</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>917873</t>
+          <t>1001687</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7025</t>
+          <t>7410</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>3198</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16617</t>
+          <t>15928</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,22 +1099,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>462</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>5191</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>8760</t>
+          <t>9412</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17800</t>
+          <t>19896</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -1177,27 +1177,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4459</t>
+          <t>4663</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1471</t>
+          <t>1627</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9156</t>
+          <t>10011</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3835</t>
+          <t>3897</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1624</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>8738</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,22 +1247,22 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>8293</t>
+          <t>8560</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4084</t>
+          <t>4466</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14670</t>
+          <t>14561</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>498656</t>
+          <t>544725</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>498656</t>
+          <t>544725</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>498656</t>
+          <t>544725</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>443579</t>
+          <t>483703</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>443579</t>
+          <t>483703</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>443579</t>
+          <t>483703</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>942235</t>
+          <t>1028428</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>942235</t>
+          <t>1028428</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>942235</t>
+          <t>1028428</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,67 +1407,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2346</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11929</t>
+          <t>11571</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>5220</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2180</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10283</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>0,52%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3960</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1645</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9355</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9394</t>
+          <t>10814</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4993</t>
+          <t>6361</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15885</t>
+          <t>18321</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2617</t>
+          <t>2764</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9912</t>
+          <t>9447</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,22 +1555,22 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>4606</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1645</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9997</t>
+          <t>9341</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,22 +1590,22 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>6730</t>
+          <t>7370</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3322</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13575</t>
+          <t>14967</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>433471</t>
+          <t>464456</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>423711</t>
+          <t>454759</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>439215</t>
+          <t>470679</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>363965</t>
+          <t>402133</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>355101</t>
+          <t>393165</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>369913</t>
+          <t>408699</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>797436</t>
+          <t>866589</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>784799</t>
+          <t>855361</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>806360</t>
+          <t>876474</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -1746,22 +1746,22 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>4552</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1556</t>
+          <t>1670</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12726</t>
+          <t>11245</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3858</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11329</t>
+          <t>11366</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>8890</t>
+          <t>8556</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4141</t>
+          <t>3818</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18145</t>
+          <t>17491</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>452</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6784</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3502</t>
+          <t>3903</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8122</t>
+          <t>9756</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,27 +1929,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5525</t>
+          <t>5859</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2431</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11380</t>
+          <t>12307</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>448578</t>
+          <t>479321</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>448578</t>
+          <t>479321</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>448578</t>
+          <t>479321</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>379397</t>
+          <t>419867</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>379397</t>
+          <t>419867</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>379397</t>
+          <t>419867</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>827975</t>
+          <t>899188</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>827975</t>
+          <t>899188</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>827975</t>
+          <t>899188</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>8393</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>4027</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16615</t>
+          <t>16027</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>573</t>
+          <t>767</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>6914</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>11035</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18435</t>
+          <t>18266</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -2202,67 +2202,67 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>6144</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1298</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>4937</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>4141</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>1186</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>4060</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2558</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6407</t>
+          <t>7924</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>631740</t>
+          <t>428453</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>609293</t>
+          <t>415887</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>650471</t>
+          <t>438850</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,67 +2350,67 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>153442</t>
+          <t>172312</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>147507</t>
+          <t>165741</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>157562</t>
+          <t>176682</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
+          <t>92,66%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>89,12%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>95,01%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>703</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>600764</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>586125</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>610996</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
           <t>92,74%</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>89,16%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>95,23%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>703</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>785182</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>764110</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>812563</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>95,18%</t>
-        </is>
-      </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>94,31%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13520</t>
+          <t>17669</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3731</t>
+          <t>10882</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>26266</t>
+          <t>27393</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4650</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12995</t>
+          <t>14783</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>21546</t>
+          <t>26572</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7533</t>
+          <t>19163</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33766</t>
+          <t>37061</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>5373</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14145</t>
+          <t>12707</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>816</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2738</t>
+          <t>2526</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t>2792</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13437</t>
+          <t>15217</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>659525</t>
+          <t>461858</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>659525</t>
+          <t>461858</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>659525</t>
+          <t>461858</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>165446</t>
+          <t>185971</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>165446</t>
+          <t>185971</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>165446</t>
+          <t>185971</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>824971</t>
+          <t>647829</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>824971</t>
+          <t>647829</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>824971</t>
+          <t>647829</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>8114</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3608</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14523</t>
+          <t>16369</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,67 +2806,67 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8496</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>4613</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16166</t>
+          <t>15767</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>16800</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>10895</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>26159</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
           <t>0,86%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>16384</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>9691</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>25756</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>19131</t>
+          <t>19796</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>11395</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34744</t>
+          <t>33420</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>6718</t>
+          <t>9447</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2593</t>
+          <t>5476</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12723</t>
+          <t>15466</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>25850</t>
+          <t>29243</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>15670</t>
+          <t>18441</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>40523</t>
+          <t>45463</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>929758</t>
+          <t>1012266</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>909839</t>
+          <t>988672</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>946122</t>
+          <t>1030610</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>933542</t>
+          <t>808491</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>918558</t>
+          <t>796851</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>950742</t>
+          <t>817322</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1863300</t>
+          <t>1820756</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1836805</t>
+          <t>1793777</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1897217</t>
+          <t>1842328</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>94,2%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>43599</t>
+          <t>53799</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32316</t>
+          <t>41861</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>58087</t>
+          <t>71942</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>16521</t>
+          <t>17888</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7578</t>
+          <t>11642</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26633</t>
+          <t>26993</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>60119</t>
+          <t>71688</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>40788</t>
+          <t>56072</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>79099</t>
+          <t>90071</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>14200</t>
+          <t>16278</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>10084</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22470</t>
+          <t>25115</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>967</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>15143</t>
+          <t>17245</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>11151</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>23623</t>
+          <t>26302</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1014801</t>
+          <t>1110443</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1014801</t>
+          <t>1110443</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1014801</t>
+          <t>1110443</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>965995</t>
+          <t>845289</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>965995</t>
+          <t>845289</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>965995</t>
+          <t>845289</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1980796</t>
+          <t>1955732</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1980796</t>
+          <t>1955732</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1980796</t>
+          <t>1955732</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1186</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6292</t>
+          <t>5928</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>9874</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4582</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13876</t>
+          <t>16477</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>9422</t>
+          <t>11060</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5498</t>
+          <t>6275</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>15632</t>
+          <t>18464</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3474</t>
+          <t>4978</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>1983</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8718</t>
+          <t>11005</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>6019</t>
+          <t>9539</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>5212</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10813</t>
+          <t>19302</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>9493</t>
+          <t>14517</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>8582</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>15630</t>
+          <t>26399</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>407706</t>
+          <t>478426</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>394029</t>
+          <t>460332</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>418439</t>
+          <t>490433</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>749957</t>
+          <t>721925</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>735937</t>
+          <t>706318</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>767882</t>
+          <t>734356</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1157663</t>
+          <t>1200351</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1139561</t>
+          <t>1178327</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1181052</t>
+          <t>1218233</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>91,73%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>24709</t>
+          <t>28874</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>16799</t>
+          <t>20007</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>36143</t>
+          <t>42918</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>36502</t>
+          <t>42041</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>24480</t>
+          <t>33311</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>45815</t>
+          <t>52697</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>61211</t>
+          <t>70915</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>46243</t>
+          <t>57777</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>75863</t>
+          <t>87593</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -3905,102 +3905,102 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>12682</t>
+          <t>18375</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>11013</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>21209</t>
+          <t>28690</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>5,39%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>12798</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>7974</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>20417</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>31173</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>22180</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>43241</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
           <t>1,67%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>10683</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>6050</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>18215</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>23365</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>15683</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>32921</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,26%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>449687</t>
+          <t>531839</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>449687</t>
+          <t>531839</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>449687</t>
+          <t>531839</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>811466</t>
+          <t>796178</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>811466</t>
+          <t>796178</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>811466</t>
+          <t>796178</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1261153</t>
+          <t>1328017</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1261153</t>
+          <t>1328017</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1261153</t>
+          <t>1328017</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2553</t>
+          <t>2549</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>9717</t>
+          <t>9832</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2522</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>9591</t>
+          <t>9966</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -4283,22 +4283,22 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>11676</t>
+          <t>12501</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>8008</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>18273</t>
+          <t>18889</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>11676</t>
+          <t>12501</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>7675</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>17901</t>
+          <t>19439</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>224226</t>
+          <t>216246</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>211374</t>
+          <t>200716</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>231511</t>
+          <t>225122</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>675538</t>
+          <t>749758</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>661796</t>
+          <t>734545</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>686040</t>
+          <t>761441</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>899765</t>
+          <t>966004</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>883724</t>
+          <t>944936</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>913744</t>
+          <t>981207</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,32%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>8126</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>3039</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>13164</t>
+          <t>18947</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>23380</t>
+          <t>27884</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>16096</t>
+          <t>19650</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>34961</t>
+          <t>39989</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>28307</t>
+          <t>36010</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>19314</t>
+          <t>25608</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>40504</t>
+          <t>50075</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -4587,102 +4587,102 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>10385</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2746</t>
+          <t>4056</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>20728</t>
+          <t>25309</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>10,78%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>10081</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>5520</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>18201</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>20466</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>12059</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>35564</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
           <t>1,16%</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>8,73%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>8536</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>4912</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>14920</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>16858</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>9923</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>28422</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>237475</t>
+          <t>234756</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>237475</t>
+          <t>234756</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>237475</t>
+          <t>234756</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>724214</t>
+          <t>805578</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>724214</t>
+          <t>805578</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>724214</t>
+          <t>805578</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>961690</t>
+          <t>1040334</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>961690</t>
+          <t>1040334</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>961690</t>
+          <t>1040334</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>28465</t>
+          <t>29493</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>18225</t>
+          <t>21058</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>40874</t>
+          <t>42464</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>31422</t>
+          <t>36039</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>23350</t>
+          <t>26544</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>42159</t>
+          <t>46721</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>59887</t>
+          <t>65531</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>47520</t>
+          <t>51949</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>76254</t>
+          <t>80213</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -4930,102 +4930,102 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>30232</t>
+          <t>34016</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>19143</t>
+          <t>22760</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>45869</t>
+          <t>50128</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
+          <t>1,49%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>40816</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>30898</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>54614</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>74833</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>59712</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>96102</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
           <t>1,39%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>33017</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>24217</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>44004</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>63249</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>48765</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>81474</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>3104348</t>
+          <t>3121971</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3070450</t>
+          <t>3089772</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>3151794</t>
+          <t>3156176</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>3307359</t>
+          <t>3324546</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3280498</t>
+          <t>3297436</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3339146</t>
+          <t>3348367</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>6411706</t>
+          <t>6446518</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>6363163</t>
+          <t>6406950</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>6466014</t>
+          <t>6484058</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>98813</t>
+          <t>120431</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>75057</t>
+          <t>97676</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>122261</t>
+          <t>143219</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>90021</t>
+          <t>102723</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>71211</t>
+          <t>88488</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>107305</t>
+          <t>123008</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>188834</t>
+          <t>223154</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>158406</t>
+          <t>197580</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>216998</t>
+          <t>252081</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>46866</t>
+          <t>57030</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>32664</t>
+          <t>43282</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>62904</t>
+          <t>74953</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>28278</t>
+          <t>32462</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>19796</t>
+          <t>23798</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>38362</t>
+          <t>45265</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>75145</t>
+          <t>89492</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>58394</t>
+          <t>72650</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>94083</t>
+          <t>109102</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>3308723</t>
+          <t>3362941</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>3308723</t>
+          <t>3362941</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>3308723</t>
+          <t>3362941</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>3490098</t>
+          <t>3536587</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>3490098</t>
+          <t>3536587</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3490098</t>
+          <t>3536587</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>6798821</t>
+          <t>6899528</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>6798821</t>
+          <t>6899528</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>6798821</t>
+          <t>6899528</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
